--- a/excel_reports/backtest_compare/s17/compare_s17_M1_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s17/compare_s17_M1_20260528_0800_20260608_1000.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-15 11:09:22</t>
+          <t>2026-06-18 17:01:20</t>
         </is>
       </c>
     </row>

--- a/excel_reports/backtest_compare/s17/compare_s17_M1_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s17/compare_s17_M1_20260528_0800_20260608_1000.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-18 17:01:20</t>
+          <t>2026-06-19 17:10:33</t>
         </is>
       </c>
     </row>
@@ -6954,10 +6954,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -7148,66 +7148,8 @@
         <v>46178.87430555555</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>46170.74375</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>46178.87430555555</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>-3.44</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>46170.59861111111</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>46176.71388888889</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>